--- a/thaco/color/BANG LUONG MAU 1_Office_color.xlsx
+++ b/thaco/color/BANG LUONG MAU 1_Office_color.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D146B0-57A7-9641-9AC5-93B309EE99A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F84524-D3E7-FB42-9D1A-F707E9BA58F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38400" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
